--- a/stories/arbres/TREE-TMP-003.xlsx
+++ b/stories/arbres/TREE-TMP-003.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maya est à la ferme, avec maman. Maman dit : certains jours, c'est l'école. Mercredi, souvent à la maison. Samedi, à la maison. Dimanche, à la maison. Maya caresse le bois de la barrière. Mercredi. Samedi. Dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
+          <t>Maya est à la ferme, avec maman. Certains jours, c'est l'école. Mercredi, souvent à la maison. Samedi, à la maison. Dimanche, à la maison. Maya caresse le bois de la barrière. Mercredi. Samedi. Dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maya est à la ferme, avec maman.
+maman|Certains jours, c'est l'école. Mercredi, souvent à la maison. Samedi, à la maison. Dimanche, à la maison.
+narrateur|Maya caresse le bois de la barrière. Mercredi. Samedi. Dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1540,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maya regarde le chat. Maman dit : mercredi, on reste souvent à la maison. Samedi aussi. Dimanche aussi. Le chat miaule. Maya répète : mercredi. Mercredi, samedi, dimanche : souvent à la maison.</t>
+          <t>Maya regarde le chat. Mercredi, on reste souvent à la maison. Samedi aussi. Dimanche aussi. Le chat miaule. Maya répète : mercredi. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1678,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maya regarde le chat.
+maman|Mercredi, on reste souvent à la maison. Samedi aussi. Dimanche aussi.
+narrateur|Le chat miaule. Maya répète : mercredi. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Quel jour, souvent à la maison ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a dit mercredi. Maman a dit samedi et dimanche. À la maison. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2225,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2392,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers le bac à sable. Le lait est froid dans le verre. Au bac à sable, Maya dessine un M. Mercredi. Puis samedi, dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2529,6 +2585,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2693,6 +2754,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton rouge. La lumière est claire. On respire, un, deux. Mercredi, samedi, dimanche : souvent à la maison. Pas d'école ces jours-là, souvent. Mercredi, samedi, dimanche : souvent à la maison. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2921,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3088,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton bleu. Des miettes dorment sur la table. On referme le sac. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maman serre Maya tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3255,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3422,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton vert. Un chat miaule une fois. On essuie une miette. Mercredi, samedi, dimanche : souvent à la maison. On a nommé mercredi. Mercredi, samedi, dimanche : souvent à la maison. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3589,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3618,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Maya va vers le toboggan. Le tissu est tout doux. Au toboggan, maman dit : samedi on reviendra. Mercredi aussi. Dimanche à la maison. Mercredi, samedi, dimanche : souvent à la maison.</t>
+          <t>Maya va vers le toboggan. Le tissu est tout doux. Au toboggan, Samedi on reviendra. Mercredi aussi. Dimanche à la maison. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3756,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers le toboggan. Le tissu est tout doux. Au toboggan,
+maman|Samedi on reviendra. Mercredi aussi. Dimanche à la maison. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3952,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3879,7 +3981,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Maya pose un jeton rouge. Les chaussures font toc toc. On met le doudou près. Mercredi, samedi, dimanche : souvent à la maison. Le week-end, c'est samedi et dimanche. Mercredi, samedi, dimanche : souvent à la maison. Maya range. Maman dit : c'est bien.</t>
+          <t>Maya pose un jeton rouge. Les chaussures font toc toc. On met le doudou près. Mercredi, samedi, dimanche : souvent à la maison. Le week-end, c'est samedi et dimanche. Mercredi, samedi, dimanche : souvent à la maison. Maya range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4017,6 +4119,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton rouge. Les chaussures font toc toc. On met le doudou près. Mercredi, samedi, dimanche : souvent à la maison. Le week-end, c'est samedi et dimanche. Mercredi, samedi, dimanche : souvent à la maison. Maya range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4287,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4454,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton bleu. La couverture est douce. On lace les chaussures. Mercredi, samedi, dimanche : souvent à la maison. Pas d'école ces jours-là, souvent. Mercredi, samedi, dimanche : souvent à la maison. On souffle. Maya sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4621,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4788,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton vert. Une cloche tinte au loin. On met le manteau. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maya prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4955,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5122,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers les balançoires. Le bois sent le chaud. Aux balançoires, Maya chante : mercredi, samedi, dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5177,6 +5315,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5341,6 +5484,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton rouge. Le bois sent le chaud. On boit une gorgée. Mercredi, samedi, dimanche : souvent à la maison. On a nommé mercredi. Mercredi, samedi, dimanche : souvent à la maison. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5651,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5665,6 +5818,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton bleu. Une goutte tombe, ploc. On feuillette le livre. Mercredi, samedi, dimanche : souvent à la maison. Le week-end, c'est samedi et dimanche. Mercredi, samedi, dimanche : souvent à la maison. Maman serre Maya tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5985,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5989,6 +6152,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton vert. Le savon sent la fleur. On referme le livre. Mercredi, samedi, dimanche : souvent à la maison. Pas d'école ces jours-là, souvent. Mercredi, samedi, dimanche : souvent à la maison. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6319,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6348,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Maya regarde le chien. Le chien s'assoit. Maman dit : samedi, pas d'école. Dimanche non plus. Mercredi, souvent à la maison. Maya dit : samedi. Mercredi, samedi, dimanche : souvent à la maison.</t>
+          <t>Maya regarde le chien. Le chien s'assoit. Samedi, pas d'école. Dimanche non plus. Mercredi, souvent à la maison. Samedi. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6486,13 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Maya regarde le chien. Le chien s'assoit.
+maman|Samedi, pas d'école. Dimanche non plus. Mercredi, souvent à la maison.
+enfant-f|Samedi. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6493,6 +6673,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Samedi, on est où souvent ?</t>
         </is>
       </c>
     </row>
@@ -6661,6 +6846,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Samedi, dimanche. Mercredi aussi, souvent. Maya a retenu. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6847,6 +7037,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7009,6 +7204,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers le bac à sable. Le sol est un peu frais. Le sable est tiède. Maya dit mercredi. Maman ajoute samedi, dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7199,6 +7399,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7223,7 +7428,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Maya pose un jeton rouge. Le tissu est tout doux. On pose le ballon. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maya range. Maman dit : c'est bien.</t>
+          <t>Maya pose un jeton rouge. Le tissu est tout doux. On pose le ballon. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maya range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7361,6 +7566,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton rouge. Le tissu est tout doux. On pose le ballon. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maya range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7523,6 +7734,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7685,6 +7901,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton bleu. Une cuillère tinte. On secoue le sable. Mercredi, samedi, dimanche : souvent à la maison. On a nommé mercredi. Mercredi, samedi, dimanche : souvent à la maison. On souffle. Maya sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7847,6 +8068,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8009,6 +8235,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton vert. Le sable est tiède. On caresse le tissu. Mercredi, samedi, dimanche : souvent à la maison. Le week-end, c'est samedi et dimanche. Mercredi, samedi, dimanche : souvent à la maison. Maya prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8171,6 +8402,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8333,6 +8569,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers le toboggan. Un pigeon roucoule. Maya glisse, doux. Samedi. Dimanche. Mercredi à la maison. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8521,6 +8762,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8685,6 +8931,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton rouge. Un rire court, tout petit. On tend la main. Mercredi, samedi, dimanche : souvent à la maison. Pas d'école ces jours-là, souvent. Mercredi, samedi, dimanche : souvent à la maison. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8847,6 +9098,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9009,6 +9265,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton bleu. Le papier froisse, chut. On chante un petit air. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maman serre Maya tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9171,6 +9432,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9333,6 +9599,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton vert. L'herbe chatouille le mollet. On compte jusqu'à trois. Mercredi, samedi, dimanche : souvent à la maison. On a nommé mercredi. Mercredi, samedi, dimanche : souvent à la maison. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9495,6 +9766,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9657,6 +9933,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers les balançoires. L'eau fait un petit bruit. La balançoire va, vient. Maman dit dimanche. Puis mercredi, samedi. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9847,6 +10128,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9871,7 +10157,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Maya pose un jeton rouge. Un pigeon roucoule. On montre du doigt. Mercredi, samedi, dimanche : souvent à la maison. Le week-end, c'est samedi et dimanche. Mercredi, samedi, dimanche : souvent à la maison. Maya range. Maman dit : c'est bien.</t>
+          <t>Maya pose un jeton rouge. Un pigeon roucoule. On montre du doigt. Mercredi, samedi, dimanche : souvent à la maison. Le week-end, c'est samedi et dimanche. Mercredi, samedi, dimanche : souvent à la maison. Maya range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10009,6 +10295,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton rouge. Un pigeon roucoule. On montre du doigt. Mercredi, samedi, dimanche : souvent à la maison. Le week-end, c'est samedi et dimanche. Mercredi, samedi, dimanche : souvent à la maison. Maya range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10171,6 +10463,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10333,6 +10630,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton bleu. La fenêtre vibre un peu. On range la chaise. Mercredi, samedi, dimanche : souvent à la maison. Pas d'école ces jours-là, souvent. Mercredi, samedi, dimanche : souvent à la maison. On souffle. Maya sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10495,6 +10797,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10657,6 +10964,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton vert. Le lait est froid dans le verre. On range un objet. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maya prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10819,6 +11131,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10843,7 +11160,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Maya regarde la poule. La poule picore. Maman dit : dimanche, on est à la maison. Mercredi aussi, souvent. Samedi aussi. Maya dit : dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
+          <t>Maya regarde la poule. La poule picore. Dimanche, on est à la maison. Mercredi aussi, souvent. Samedi aussi. Dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10981,6 +11298,13 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Maya regarde la poule. La poule picore.
+maman|Dimanche, on est à la maison. Mercredi aussi, souvent. Samedi aussi.
+enfant-f|Dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11161,6 +11485,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Après samedi, c'est quel jour à la maison ?</t>
         </is>
       </c>
     </row>
@@ -11329,6 +11658,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Dimanche à la maison. Mercredi. Samedi. Maya sourit. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11515,6 +11849,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11677,6 +12016,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers le bac à sable. L'herbe chatouille le mollet. Maya enterre une feuille. Mercredi. Samedi. Dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11865,6 +12209,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12029,6 +12378,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton rouge. La corde du sac est rêche. On se tient la main. Mercredi, samedi, dimanche : souvent à la maison. On a nommé mercredi. Mercredi, samedi, dimanche : souvent à la maison. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12191,6 +12545,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12353,6 +12712,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton bleu. Le savon mousse entre les doigts. On dit merci. Mercredi, samedi, dimanche : souvent à la maison. Le week-end, c'est samedi et dimanche. Mercredi, samedi, dimanche : souvent à la maison. Maman serre Maya tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12515,6 +12879,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12677,6 +13046,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton vert. Un ruisseau chante. On souffle doucement. Mercredi, samedi, dimanche : souvent à la maison. Pas d'école ces jours-là, souvent. Mercredi, samedi, dimanche : souvent à la maison. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12839,6 +13213,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13001,6 +13380,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers le toboggan. Le vent est doux sur la joue. En haut du toboggan, maman tient la main. Samedi, dimanche, mercredi. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13191,6 +13575,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13215,7 +13604,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Maya pose un jeton rouge. La laine gratte un peu. On écoute jusqu'au bout. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maya range. Maman dit : c'est bien.</t>
+          <t>Maya pose un jeton rouge. La laine gratte un peu. On écoute jusqu'au bout. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maya range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13353,6 +13742,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton rouge. La laine gratte un peu. On écoute jusqu'au bout. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maya range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13515,6 +13910,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13677,6 +14077,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton bleu. Un pain croustille. On attend son tour. Mercredi, samedi, dimanche : souvent à la maison. On a nommé mercredi. Mercredi, samedi, dimanche : souvent à la maison. On souffle. Maya sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13839,6 +14244,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14001,6 +14411,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton vert. Le savon glisse. On sourit ensemble. Mercredi, samedi, dimanche : souvent à la maison. Le week-end, c'est samedi et dimanche. Mercredi, samedi, dimanche : souvent à la maison. Maya prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14163,6 +14578,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14325,6 +14745,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers les balançoires. Une goutte tombe, ploc. Maya s'arrête. Maman répète : mercredi, samedi, dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14513,6 +14938,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14677,6 +15107,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton rouge. Une plume vole. On pose les pieds par terre. Mercredi, samedi, dimanche : souvent à la maison. Pas d'école ces jours-là, souvent. Mercredi, samedi, dimanche : souvent à la maison. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14839,6 +15274,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15001,6 +15441,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton bleu. Le banc est lisse. On parle tout bas. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maman serre Maya tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15163,6 +15608,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15325,6 +15775,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose un jeton vert. Un grelot sonne. On range les jouets. Mercredi, samedi, dimanche : souvent à la maison. On a nommé mercredi. Mercredi, samedi, dimanche : souvent à la maison. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15487,6 +15942,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15505,7 +15965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15578,6 +16038,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-TMP-003.xlsx
+++ b/stories/arbres/TREE-TMP-003.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Maya caresse le bois de la barrière. Mercredi. Samedi. Dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -1685,6 +1696,7 @@
 narrateur|Le chat miaule. Maya répète : mercredi. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1880,7 @@
           <t>narrateur|Quel jour, souvent à la maison ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2052,7 @@
           <t>narrateur|Maya a dit mercredi. Maman a dit samedi et dimanche. À la maison. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2244,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2397,6 +2412,7 @@
           <t>narrateur|Maya va vers le bac à sable. Le lait est froid dans le verre. Au bac à sable, Maya dessine un M. Mercredi. Puis samedi, dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2592,6 +2608,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2759,6 +2776,7 @@
           <t>narrateur|Maya pose un jeton rouge. La lumière est claire. On respire, un, deux. Mercredi, samedi, dimanche : souvent à la maison. Pas d'école ces jours-là, souvent. Mercredi, samedi, dimanche : souvent à la maison. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2926,6 +2944,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3093,6 +3112,7 @@
           <t>narrateur|Maya pose un jeton bleu. Des miettes dorment sur la table. On referme le sac. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maman serre Maya tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3260,6 +3280,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3427,6 +3448,7 @@
           <t>narrateur|Maya pose un jeton vert. Un chat miaule une fois. On essuie une miette. Mercredi, samedi, dimanche : souvent à la maison. On a nommé mercredi. Mercredi, samedi, dimanche : souvent à la maison. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3594,6 +3616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3785,7 @@
 maman|Samedi on reviendra. Mercredi aussi. Dimanche à la maison. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3981,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4125,6 +4150,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4292,6 +4318,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4459,6 +4486,7 @@
           <t>narrateur|Maya pose un jeton bleu. La couverture est douce. On lace les chaussures. Mercredi, samedi, dimanche : souvent à la maison. Pas d'école ces jours-là, souvent. Mercredi, samedi, dimanche : souvent à la maison. On souffle. Maya sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4626,6 +4654,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4793,6 +4822,7 @@
           <t>narrateur|Maya pose un jeton vert. Une cloche tinte au loin. On met le manteau. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maya prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4960,6 +4990,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5127,6 +5158,7 @@
           <t>narrateur|Maya va vers les balançoires. Le bois sent le chaud. Aux balançoires, Maya chante : mercredi, samedi, dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5322,6 +5354,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5489,6 +5522,7 @@
           <t>narrateur|Maya pose un jeton rouge. Le bois sent le chaud. On boit une gorgée. Mercredi, samedi, dimanche : souvent à la maison. On a nommé mercredi. Mercredi, samedi, dimanche : souvent à la maison. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5656,6 +5690,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5823,6 +5858,7 @@
           <t>narrateur|Maya pose un jeton bleu. Une goutte tombe, ploc. On feuillette le livre. Mercredi, samedi, dimanche : souvent à la maison. Le week-end, c'est samedi et dimanche. Mercredi, samedi, dimanche : souvent à la maison. Maman serre Maya tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5990,6 +6026,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6157,6 +6194,7 @@
           <t>narrateur|Maya pose un jeton vert. Le savon sent la fleur. On referme le livre. Mercredi, samedi, dimanche : souvent à la maison. Pas d'école ces jours-là, souvent. Mercredi, samedi, dimanche : souvent à la maison. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6324,6 +6362,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6493,6 +6532,11 @@
 enfant-f|Samedi. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6680,6 +6724,7 @@
           <t>narrateur|Samedi, on est où souvent ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6851,6 +6896,7 @@
           <t>narrateur|Samedi, dimanche. Mercredi aussi, souvent. Maya a retenu. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7042,6 +7088,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7209,6 +7256,7 @@
           <t>narrateur|Maya va vers le bac à sable. Le sol est un peu frais. Le sable est tiède. Maya dit mercredi. Maman ajoute samedi, dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7404,6 +7452,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7572,6 +7621,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7739,6 +7789,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7906,6 +7957,7 @@
           <t>narrateur|Maya pose un jeton bleu. Une cuillère tinte. On secoue le sable. Mercredi, samedi, dimanche : souvent à la maison. On a nommé mercredi. Mercredi, samedi, dimanche : souvent à la maison. On souffle. Maya sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8073,6 +8125,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8240,6 +8293,7 @@
           <t>narrateur|Maya pose un jeton vert. Le sable est tiède. On caresse le tissu. Mercredi, samedi, dimanche : souvent à la maison. Le week-end, c'est samedi et dimanche. Mercredi, samedi, dimanche : souvent à la maison. Maya prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8407,6 +8461,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8574,6 +8629,7 @@
           <t>narrateur|Maya va vers le toboggan. Un pigeon roucoule. Maya glisse, doux. Samedi. Dimanche. Mercredi à la maison. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8769,6 +8825,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8936,6 +8993,7 @@
           <t>narrateur|Maya pose un jeton rouge. Un rire court, tout petit. On tend la main. Mercredi, samedi, dimanche : souvent à la maison. Pas d'école ces jours-là, souvent. Mercredi, samedi, dimanche : souvent à la maison. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9103,6 +9161,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9270,6 +9329,7 @@
           <t>narrateur|Maya pose un jeton bleu. Le papier froisse, chut. On chante un petit air. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maman serre Maya tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9437,6 +9497,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9604,6 +9665,7 @@
           <t>narrateur|Maya pose un jeton vert. L'herbe chatouille le mollet. On compte jusqu'à trois. Mercredi, samedi, dimanche : souvent à la maison. On a nommé mercredi. Mercredi, samedi, dimanche : souvent à la maison. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9771,6 +9833,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9938,6 +10001,7 @@
           <t>narrateur|Maya va vers les balançoires. L'eau fait un petit bruit. La balançoire va, vient. Maman dit dimanche. Puis mercredi, samedi. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10133,6 +10197,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10301,6 +10366,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10468,6 +10534,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10635,6 +10702,7 @@
           <t>narrateur|Maya pose un jeton bleu. La fenêtre vibre un peu. On range la chaise. Mercredi, samedi, dimanche : souvent à la maison. Pas d'école ces jours-là, souvent. Mercredi, samedi, dimanche : souvent à la maison. On souffle. Maya sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10802,6 +10870,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10969,6 +11038,7 @@
           <t>narrateur|Maya pose un jeton vert. Le lait est froid dans le verre. On range un objet. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maya prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11136,6 +11206,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11305,6 +11376,7 @@
 enfant-f|Dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11492,6 +11564,7 @@
           <t>narrateur|Après samedi, c'est quel jour à la maison ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11663,6 +11736,7 @@
           <t>narrateur|Dimanche à la maison. Mercredi. Samedi. Maya sourit. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11854,6 +11928,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12021,6 +12096,7 @@
           <t>narrateur|Maya va vers le bac à sable. L'herbe chatouille le mollet. Maya enterre une feuille. Mercredi. Samedi. Dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12216,6 +12292,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12383,6 +12460,7 @@
           <t>narrateur|Maya pose un jeton rouge. La corde du sac est rêche. On se tient la main. Mercredi, samedi, dimanche : souvent à la maison. On a nommé mercredi. Mercredi, samedi, dimanche : souvent à la maison. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12550,6 +12628,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12717,6 +12796,7 @@
           <t>narrateur|Maya pose un jeton bleu. Le savon mousse entre les doigts. On dit merci. Mercredi, samedi, dimanche : souvent à la maison. Le week-end, c'est samedi et dimanche. Mercredi, samedi, dimanche : souvent à la maison. Maman serre Maya tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12884,6 +12964,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13051,6 +13132,7 @@
           <t>narrateur|Maya pose un jeton vert. Un ruisseau chante. On souffle doucement. Mercredi, samedi, dimanche : souvent à la maison. Pas d'école ces jours-là, souvent. Mercredi, samedi, dimanche : souvent à la maison. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13218,6 +13300,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13385,6 +13468,7 @@
           <t>narrateur|Maya va vers le toboggan. Le vent est doux sur la joue. En haut du toboggan, maman tient la main. Samedi, dimanche, mercredi. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13580,6 +13664,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13748,6 +13833,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13915,6 +14001,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14082,6 +14169,7 @@
           <t>narrateur|Maya pose un jeton bleu. Un pain croustille. On attend son tour. Mercredi, samedi, dimanche : souvent à la maison. On a nommé mercredi. Mercredi, samedi, dimanche : souvent à la maison. On souffle. Maya sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14249,6 +14337,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14416,6 +14505,7 @@
           <t>narrateur|Maya pose un jeton vert. Le savon glisse. On sourit ensemble. Mercredi, samedi, dimanche : souvent à la maison. Le week-end, c'est samedi et dimanche. Mercredi, samedi, dimanche : souvent à la maison. Maya prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14583,6 +14673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14750,6 +14841,7 @@
           <t>narrateur|Maya va vers les balançoires. Une goutte tombe, ploc. Maya s'arrête. Maman répète : mercredi, samedi, dimanche. Mercredi, samedi, dimanche : souvent à la maison.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14945,6 +15037,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15112,6 +15205,7 @@
           <t>narrateur|Maya pose un jeton rouge. Une plume vole. On pose les pieds par terre. Mercredi, samedi, dimanche : souvent à la maison. Pas d'école ces jours-là, souvent. Mercredi, samedi, dimanche : souvent à la maison. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15279,6 +15373,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15446,6 +15541,7 @@
           <t>narrateur|Maya pose un jeton bleu. Le banc est lisse. On parle tout bas. Mercredi, samedi, dimanche : souvent à la maison. La maison attend. Mercredi, samedi, dimanche : souvent à la maison. Maman serre Maya tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15613,6 +15709,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15780,6 +15877,7 @@
           <t>narrateur|Maya pose un jeton vert. Un grelot sonne. On range les jouets. Mercredi, samedi, dimanche : souvent à la maison. On a nommé mercredi. Mercredi, samedi, dimanche : souvent à la maison. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15947,6 +16045,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15965,7 +16064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16045,6 +16144,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16246,6 +16359,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
